--- a/output/graficos_nacionales/plot_nacional_e_basneta_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_basneta_a_2020.xlsx
@@ -85,12 +85,6 @@
     <t xml:space="preserve">Río Ibáñez</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11302</t>
   </si>
   <si>
@@ -115,12 +109,6 @@
     <t xml:space="preserve">Cochrane</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">12101</t>
   </si>
   <si>
@@ -544,6 +532,12 @@
     <t xml:space="preserve">Olivar</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">5403</t>
   </si>
   <si>
@@ -1441,6 +1435,12 @@
     <t xml:space="preserve">Iquique</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">2203</t>
   </si>
   <si>
@@ -2116,7 +2116,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:21</t>
+    <t xml:space="preserve">2026-09-09 20:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2692,7 +2692,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>97.67</v>
+        <v>97.65</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>16</v>
@@ -2703,10 +2703,10 @@
         <v>2020</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>24</v>
@@ -2724,7 +2724,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>97.65</v>
+        <v>97.53</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>16</v>
@@ -2735,10 +2735,10 @@
         <v>2020</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>26</v>
@@ -2756,7 +2756,7 @@
         <v>15</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>97.53</v>
+        <v>97.11</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>16</v>
@@ -2788,7 +2788,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>97.11</v>
+        <v>97.09</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>16</v>
@@ -2799,10 +2799,10 @@
         <v>2020</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>30</v>
@@ -2820,7 +2820,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>97.09</v>
+        <v>95.95</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>16</v>
@@ -2852,7 +2852,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>96.92</v>
+        <v>95.38</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>16</v>
@@ -2884,7 +2884,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>95.95</v>
+        <v>95.25</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>16</v>
@@ -2895,10 +2895,10 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>36</v>
@@ -2916,7 +2916,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>95.38</v>
+        <v>95.05</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>16</v>
@@ -2927,10 +2927,10 @@
         <v>2020</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>38</v>
@@ -2948,7 +2948,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>95.25</v>
+        <v>95</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>16</v>
@@ -2959,10 +2959,10 @@
         <v>2020</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>40</v>
@@ -2980,7 +2980,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>95.05</v>
+        <v>94.46</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>16</v>
@@ -2991,28 +2991,28 @@
         <v>2020</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>95</v>
+        <v>99.77</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>16</v>
@@ -3023,28 +3023,28 @@
         <v>2020</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>94.46</v>
+        <v>99.34</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>16</v>
@@ -3055,28 +3055,28 @@
         <v>2020</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>99.77</v>
+        <v>98.13</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>16</v>
@@ -3090,25 +3090,25 @@
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>99.34</v>
+        <v>97.99</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>16</v>
@@ -3119,10 +3119,10 @@
         <v>2020</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>55</v>
@@ -3131,16 +3131,16 @@
         <v>56</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>98.13</v>
+        <v>97.97</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>16</v>
@@ -3154,7 +3154,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>57</v>
@@ -3163,16 +3163,16 @@
         <v>58</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>97.99</v>
+        <v>97.91</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>16</v>
@@ -3183,28 +3183,28 @@
         <v>2020</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>97.97</v>
+        <v>97.9</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>16</v>
@@ -3215,28 +3215,28 @@
         <v>2020</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>97.91</v>
+        <v>97.87</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
@@ -3250,7 +3250,7 @@
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>64</v>
@@ -3259,16 +3259,16 @@
         <v>65</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>97.9</v>
+        <v>97.83</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
@@ -3279,10 +3279,10 @@
         <v>2020</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>66</v>
@@ -3291,16 +3291,16 @@
         <v>67</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>97.87</v>
+        <v>97.77</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
@@ -3314,7 +3314,7 @@
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>68</v>
@@ -3323,16 +3323,16 @@
         <v>69</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>97.83</v>
+        <v>97.76</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>16</v>
@@ -3346,7 +3346,7 @@
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>70</v>
@@ -3355,16 +3355,16 @@
         <v>71</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>97.77</v>
+        <v>97.75</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
@@ -3375,10 +3375,10 @@
         <v>2020</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>72</v>
@@ -3387,16 +3387,16 @@
         <v>73</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>97.76</v>
+        <v>97.71</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>16</v>
@@ -3407,10 +3407,10 @@
         <v>2020</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>74</v>
@@ -3419,16 +3419,16 @@
         <v>75</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>97.75</v>
+        <v>97.64</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>16</v>
@@ -3439,10 +3439,10 @@
         <v>2020</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>76</v>
@@ -3451,16 +3451,16 @@
         <v>77</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>97.71</v>
+        <v>97.6</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>16</v>
@@ -3471,10 +3471,10 @@
         <v>2020</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>78</v>
@@ -3483,16 +3483,16 @@
         <v>79</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>97.64</v>
+        <v>97.58</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>16</v>
@@ -3503,10 +3503,10 @@
         <v>2020</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>80</v>
@@ -3515,16 +3515,16 @@
         <v>81</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>97.6</v>
+        <v>97.54</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>16</v>
@@ -3535,10 +3535,10 @@
         <v>2020</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>82</v>
@@ -3547,16 +3547,16 @@
         <v>83</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>97.58</v>
+        <v>97.51</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>16</v>
@@ -3567,10 +3567,10 @@
         <v>2020</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>84</v>
@@ -3579,16 +3579,16 @@
         <v>85</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>97.54</v>
+        <v>97.45</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>16</v>
@@ -3599,10 +3599,10 @@
         <v>2020</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>86</v>
@@ -3611,16 +3611,16 @@
         <v>87</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>97.51</v>
+        <v>97.4</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>16</v>
@@ -3631,10 +3631,10 @@
         <v>2020</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>88</v>
@@ -3643,16 +3643,16 @@
         <v>89</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>97.45</v>
+        <v>97.38</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>16</v>
@@ -3666,7 +3666,7 @@
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>90</v>
@@ -3675,16 +3675,16 @@
         <v>91</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>97.4</v>
+        <v>97.29</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>16</v>
@@ -3695,10 +3695,10 @@
         <v>2020</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>92</v>
@@ -3707,16 +3707,16 @@
         <v>93</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>97.38</v>
+        <v>97.24</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>16</v>
@@ -3730,7 +3730,7 @@
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>94</v>
@@ -3739,16 +3739,16 @@
         <v>95</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>97.29</v>
+        <v>97.17</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>16</v>
@@ -3759,10 +3759,10 @@
         <v>2020</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>96</v>
@@ -3771,16 +3771,16 @@
         <v>97</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>97.24</v>
+        <v>97.16</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>16</v>
@@ -3794,7 +3794,7 @@
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>98</v>
@@ -3803,16 +3803,16 @@
         <v>99</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>97.17</v>
+        <v>97.16</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>16</v>
@@ -3823,10 +3823,10 @@
         <v>2020</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>100</v>
@@ -3835,16 +3835,16 @@
         <v>101</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>97.16</v>
+        <v>97.15</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>16</v>
@@ -3855,28 +3855,28 @@
         <v>2020</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>97.16</v>
+        <v>97.13</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>16</v>
@@ -3890,25 +3890,25 @@
         <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>97.15</v>
+        <v>97.12</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>16</v>
@@ -3919,10 +3919,10 @@
         <v>2020</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>107</v>
@@ -3931,16 +3931,16 @@
         <v>108</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>97.13</v>
+        <v>97.02</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>16</v>
@@ -3951,10 +3951,10 @@
         <v>2020</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>109</v>
@@ -3963,16 +3963,16 @@
         <v>110</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>97.12</v>
+        <v>97.02</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>16</v>
@@ -3983,10 +3983,10 @@
         <v>2020</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>111</v>
@@ -3995,16 +3995,16 @@
         <v>112</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>97.02</v>
+        <v>97</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>16</v>
@@ -4015,10 +4015,10 @@
         <v>2020</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>113</v>
@@ -4027,16 +4027,16 @@
         <v>114</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>97.02</v>
+        <v>96.96</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
@@ -4047,10 +4047,10 @@
         <v>2020</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>115</v>
@@ -4059,16 +4059,16 @@
         <v>116</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>97</v>
+        <v>96.95</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>16</v>
@@ -4079,10 +4079,10 @@
         <v>2020</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>117</v>
@@ -4091,16 +4091,16 @@
         <v>118</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>96.96</v>
+        <v>96.93</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>16</v>
@@ -4111,10 +4111,10 @@
         <v>2020</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>119</v>
@@ -4123,16 +4123,16 @@
         <v>120</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>96.95</v>
+        <v>96.93</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>16</v>
@@ -4143,10 +4143,10 @@
         <v>2020</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>121</v>
@@ -4155,16 +4155,16 @@
         <v>122</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>96.93</v>
+        <v>96.91</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>16</v>
@@ -4175,10 +4175,10 @@
         <v>2020</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>123</v>
@@ -4187,16 +4187,16 @@
         <v>124</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>96.93</v>
+        <v>96.9</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>16</v>
@@ -4207,10 +4207,10 @@
         <v>2020</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>125</v>
@@ -4219,16 +4219,16 @@
         <v>126</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>96.91</v>
+        <v>96.89</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>16</v>
@@ -4239,10 +4239,10 @@
         <v>2020</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>127</v>
@@ -4251,16 +4251,16 @@
         <v>128</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>96.9</v>
+        <v>96.85</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>16</v>
@@ -4271,10 +4271,10 @@
         <v>2020</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>129</v>
@@ -4283,16 +4283,16 @@
         <v>130</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>96.89</v>
+        <v>96.85</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>16</v>
@@ -4303,10 +4303,10 @@
         <v>2020</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>131</v>
@@ -4315,16 +4315,16 @@
         <v>132</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>96.85</v>
+        <v>96.84</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>16</v>
@@ -4335,10 +4335,10 @@
         <v>2020</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>133</v>
@@ -4347,16 +4347,16 @@
         <v>134</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>96.85</v>
+        <v>96.81</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>16</v>
@@ -4367,10 +4367,10 @@
         <v>2020</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>135</v>
@@ -4379,16 +4379,16 @@
         <v>136</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>96.84</v>
+        <v>96.81</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>16</v>
@@ -4399,10 +4399,10 @@
         <v>2020</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>137</v>
@@ -4411,10 +4411,10 @@
         <v>138</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
@@ -4431,10 +4431,10 @@
         <v>2020</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>139</v>
@@ -4443,16 +4443,16 @@
         <v>140</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>96.81</v>
+        <v>96.79</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>16</v>
@@ -4463,10 +4463,10 @@
         <v>2020</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>141</v>
@@ -4475,16 +4475,16 @@
         <v>142</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>96.81</v>
+        <v>96.77</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>16</v>
@@ -4495,10 +4495,10 @@
         <v>2020</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>143</v>
@@ -4507,16 +4507,16 @@
         <v>144</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>96.79</v>
+        <v>96.76</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>16</v>
@@ -4527,10 +4527,10 @@
         <v>2020</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>145</v>
@@ -4539,16 +4539,16 @@
         <v>146</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>96.77</v>
+        <v>96.73</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>16</v>
@@ -4562,7 +4562,7 @@
         <v>6</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>147</v>
@@ -4571,16 +4571,16 @@
         <v>148</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>96.76</v>
+        <v>96.72</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>16</v>
@@ -4591,10 +4591,10 @@
         <v>2020</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>149</v>
@@ -4603,16 +4603,16 @@
         <v>150</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>96.73</v>
+        <v>96.71</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>16</v>
@@ -4623,10 +4623,10 @@
         <v>2020</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>151</v>
@@ -4635,16 +4635,16 @@
         <v>152</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>96.72</v>
+        <v>96.71</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>16</v>
@@ -4655,10 +4655,10 @@
         <v>2020</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>153</v>
@@ -4667,16 +4667,16 @@
         <v>154</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>96.71</v>
+        <v>96.68</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>16</v>
@@ -4687,10 +4687,10 @@
         <v>2020</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>155</v>
@@ -4699,16 +4699,16 @@
         <v>156</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>96.71</v>
+        <v>96.68</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>16</v>
@@ -4719,10 +4719,10 @@
         <v>2020</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>157</v>
@@ -4731,16 +4731,16 @@
         <v>158</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>96.68</v>
+        <v>96.65</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>16</v>
@@ -4754,7 +4754,7 @@
         <v>7</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>159</v>
@@ -4763,16 +4763,16 @@
         <v>160</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>96.68</v>
+        <v>96.65</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>16</v>
@@ -4783,10 +4783,10 @@
         <v>2020</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>161</v>
@@ -4795,16 +4795,16 @@
         <v>162</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>96.65</v>
+        <v>96.64</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>16</v>
@@ -4815,10 +4815,10 @@
         <v>2020</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>163</v>
@@ -4827,16 +4827,16 @@
         <v>164</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>96.65</v>
+        <v>96.59</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>16</v>
@@ -4847,10 +4847,10 @@
         <v>2020</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>165</v>
@@ -4859,16 +4859,16 @@
         <v>166</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>96.64</v>
+        <v>96.56</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>16</v>
@@ -4879,10 +4879,10 @@
         <v>2020</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>167</v>
@@ -4891,16 +4891,16 @@
         <v>168</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>96.59</v>
+        <v>96.54</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>16</v>
@@ -4911,10 +4911,10 @@
         <v>2020</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>169</v>
@@ -4923,16 +4923,16 @@
         <v>170</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>96.56</v>
+        <v>96.51</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>16</v>
@@ -4943,10 +4943,10 @@
         <v>2020</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>171</v>
@@ -4955,16 +4955,16 @@
         <v>172</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>96.54</v>
+        <v>96.5</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>16</v>
@@ -4975,10 +4975,10 @@
         <v>2020</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>173</v>
@@ -4987,16 +4987,16 @@
         <v>174</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>96.51</v>
+        <v>96.49</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>16</v>
@@ -5007,10 +5007,10 @@
         <v>2020</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>175</v>
@@ -5019,16 +5019,16 @@
         <v>176</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>96.49</v>
+        <v>96.42</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>16</v>
@@ -5042,7 +5042,7 @@
         <v>6</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>177</v>
@@ -5051,10 +5051,10 @@
         <v>178</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
@@ -5071,10 +5071,10 @@
         <v>2020</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>179</v>
@@ -5083,16 +5083,16 @@
         <v>180</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>96.42</v>
+        <v>96.4</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>16</v>
@@ -5106,7 +5106,7 @@
         <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>181</v>
@@ -5115,16 +5115,16 @@
         <v>182</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>96.4</v>
+        <v>96.37</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>16</v>
@@ -5135,10 +5135,10 @@
         <v>2020</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>183</v>
@@ -5147,16 +5147,16 @@
         <v>184</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>96.37</v>
+        <v>96.36</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>16</v>
@@ -5167,10 +5167,10 @@
         <v>2020</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>185</v>
@@ -5179,16 +5179,16 @@
         <v>186</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>96.36</v>
+        <v>96.3</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>16</v>
@@ -5199,10 +5199,10 @@
         <v>2020</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>187</v>
@@ -5211,16 +5211,16 @@
         <v>188</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>96.3</v>
+        <v>96.29</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>16</v>
@@ -5231,10 +5231,10 @@
         <v>2020</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>189</v>
@@ -5243,16 +5243,16 @@
         <v>190</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>96.29</v>
+        <v>96.26</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>16</v>
@@ -5266,7 +5266,7 @@
         <v>7</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>191</v>
@@ -5275,10 +5275,10 @@
         <v>192</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
@@ -5295,10 +5295,10 @@
         <v>2020</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>193</v>
@@ -5307,16 +5307,16 @@
         <v>194</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>96.26</v>
+        <v>96.22</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>16</v>
@@ -5327,10 +5327,10 @@
         <v>2020</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>195</v>
@@ -5339,16 +5339,16 @@
         <v>196</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>96.22</v>
+        <v>96.2</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>16</v>
@@ -5359,10 +5359,10 @@
         <v>2020</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>197</v>
@@ -5371,16 +5371,16 @@
         <v>198</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>96.2</v>
+        <v>96.19</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>16</v>
@@ -5391,10 +5391,10 @@
         <v>2020</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>199</v>
@@ -5403,10 +5403,10 @@
         <v>200</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
@@ -5423,10 +5423,10 @@
         <v>2020</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>201</v>
@@ -5435,16 +5435,16 @@
         <v>202</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>96.19</v>
+        <v>96.17</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>16</v>
@@ -5455,10 +5455,10 @@
         <v>2020</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>203</v>
@@ -5467,16 +5467,16 @@
         <v>204</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>96.17</v>
+        <v>96.16</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>16</v>
@@ -5487,10 +5487,10 @@
         <v>2020</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>205</v>
@@ -5499,10 +5499,10 @@
         <v>206</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
@@ -5519,10 +5519,10 @@
         <v>2020</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>207</v>
@@ -5531,16 +5531,16 @@
         <v>208</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>96.16</v>
+        <v>96.13</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>16</v>
@@ -5551,10 +5551,10 @@
         <v>2020</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>209</v>
@@ -5563,16 +5563,16 @@
         <v>210</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>96.13</v>
+        <v>96.11</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>16</v>
@@ -5583,10 +5583,10 @@
         <v>2020</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>211</v>
@@ -5595,16 +5595,16 @@
         <v>212</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>96.11</v>
+        <v>96.1</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>16</v>
@@ -5618,7 +5618,7 @@
         <v>5</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>213</v>
@@ -5627,16 +5627,16 @@
         <v>214</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>96.1</v>
+        <v>96.06</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>16</v>
@@ -5647,10 +5647,10 @@
         <v>2020</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>215</v>
@@ -5659,10 +5659,10 @@
         <v>216</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
@@ -5679,10 +5679,10 @@
         <v>2020</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>217</v>
@@ -5691,16 +5691,16 @@
         <v>218</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>96.06</v>
+        <v>96.05</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>16</v>
@@ -5711,10 +5711,10 @@
         <v>2020</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>219</v>
@@ -5723,10 +5723,10 @@
         <v>220</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
@@ -5743,10 +5743,10 @@
         <v>2020</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>221</v>
@@ -5755,16 +5755,16 @@
         <v>222</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>96.05</v>
+        <v>96.02</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>16</v>
@@ -5775,10 +5775,10 @@
         <v>2020</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>223</v>
@@ -5787,16 +5787,16 @@
         <v>224</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>96.02</v>
+        <v>96.01</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>16</v>
@@ -5810,7 +5810,7 @@
         <v>13</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>225</v>
@@ -5819,16 +5819,16 @@
         <v>226</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>96.01</v>
+        <v>95.99</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>16</v>
@@ -5842,7 +5842,7 @@
         <v>13</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>227</v>
@@ -5851,16 +5851,16 @@
         <v>228</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>95.99</v>
+        <v>95.97</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>16</v>
@@ -5874,7 +5874,7 @@
         <v>13</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>229</v>
@@ -5883,16 +5883,16 @@
         <v>230</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>95.97</v>
+        <v>95.94</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>16</v>
@@ -5903,10 +5903,10 @@
         <v>2020</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>231</v>
@@ -5915,16 +5915,16 @@
         <v>232</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>95.94</v>
+        <v>95.92</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>16</v>
@@ -5935,10 +5935,10 @@
         <v>2020</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>233</v>
@@ -5947,16 +5947,16 @@
         <v>234</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>95.92</v>
+        <v>95.91</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>16</v>
@@ -5967,10 +5967,10 @@
         <v>2020</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>235</v>
@@ -5979,16 +5979,16 @@
         <v>236</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>95.91</v>
+        <v>95.9</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>16</v>
@@ -5999,10 +5999,10 @@
         <v>2020</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>237</v>
@@ -6011,16 +6011,16 @@
         <v>238</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>95.9</v>
+        <v>95.88</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>16</v>
@@ -6031,10 +6031,10 @@
         <v>2020</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>239</v>
@@ -6043,16 +6043,16 @@
         <v>240</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>95.88</v>
+        <v>95.86</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>16</v>
@@ -6066,7 +6066,7 @@
         <v>13</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>241</v>
@@ -6075,10 +6075,10 @@
         <v>242</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
@@ -6095,10 +6095,10 @@
         <v>2020</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>243</v>
@@ -6107,16 +6107,16 @@
         <v>244</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>95.86</v>
+        <v>95.84</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>16</v>
@@ -6127,10 +6127,10 @@
         <v>2020</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>245</v>
@@ -6139,16 +6139,16 @@
         <v>246</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>95.84</v>
+        <v>95.82</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>16</v>
@@ -6159,10 +6159,10 @@
         <v>2020</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>247</v>
@@ -6171,16 +6171,16 @@
         <v>248</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>95.82</v>
+        <v>95.81</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>16</v>
@@ -6191,10 +6191,10 @@
         <v>2020</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>249</v>
@@ -6203,10 +6203,10 @@
         <v>250</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
@@ -6223,10 +6223,10 @@
         <v>2020</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>251</v>
@@ -6235,16 +6235,16 @@
         <v>252</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>95.81</v>
+        <v>95.8</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>16</v>
@@ -6258,7 +6258,7 @@
         <v>13</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>253</v>
@@ -6267,16 +6267,16 @@
         <v>254</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>95.8</v>
+        <v>95.79</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>16</v>
@@ -6290,7 +6290,7 @@
         <v>13</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>255</v>
@@ -6299,16 +6299,16 @@
         <v>256</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>95.79</v>
+        <v>95.77</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>16</v>
@@ -6319,10 +6319,10 @@
         <v>2020</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>257</v>
@@ -6331,16 +6331,16 @@
         <v>258</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>95.77</v>
+        <v>95.75</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>16</v>
@@ -6351,10 +6351,10 @@
         <v>2020</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>259</v>
@@ -6363,16 +6363,16 @@
         <v>260</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>95.75</v>
+        <v>95.74</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>16</v>
@@ -6383,10 +6383,10 @@
         <v>2020</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>261</v>
@@ -6395,16 +6395,16 @@
         <v>262</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>95.74</v>
+        <v>95.73</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>16</v>
@@ -6415,10 +6415,10 @@
         <v>2020</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>263</v>
@@ -6427,16 +6427,16 @@
         <v>264</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>95.73</v>
+        <v>95.7</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>16</v>
@@ -6447,10 +6447,10 @@
         <v>2020</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>265</v>
@@ -6459,16 +6459,16 @@
         <v>266</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>95.7</v>
+        <v>95.67</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>16</v>
@@ -6479,10 +6479,10 @@
         <v>2020</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>267</v>
@@ -6491,16 +6491,16 @@
         <v>268</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>95.67</v>
+        <v>95.64</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>16</v>
@@ -6514,7 +6514,7 @@
         <v>6</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>269</v>
@@ -6523,10 +6523,10 @@
         <v>270</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
@@ -6546,7 +6546,7 @@
         <v>6</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>271</v>
@@ -6555,16 +6555,16 @@
         <v>272</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>95.64</v>
+        <v>95.54</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>16</v>
@@ -6575,10 +6575,10 @@
         <v>2020</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>273</v>
@@ -6587,16 +6587,16 @@
         <v>274</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>95.54</v>
+        <v>95.51</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>16</v>
@@ -6610,7 +6610,7 @@
         <v>5</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>275</v>
@@ -6619,16 +6619,16 @@
         <v>276</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>95.51</v>
+        <v>95.49</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>16</v>
@@ -6642,7 +6642,7 @@
         <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>277</v>
@@ -6651,16 +6651,16 @@
         <v>278</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>95.49</v>
+        <v>95.47</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>16</v>
@@ -6674,7 +6674,7 @@
         <v>5</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>279</v>
@@ -6683,16 +6683,16 @@
         <v>280</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>95.47</v>
+        <v>95.46</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>16</v>
@@ -6703,10 +6703,10 @@
         <v>2020</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>281</v>
@@ -6715,10 +6715,10 @@
         <v>282</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
@@ -6735,10 +6735,10 @@
         <v>2020</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>283</v>
@@ -6747,16 +6747,16 @@
         <v>284</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>95.46</v>
+        <v>95.42</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>16</v>
@@ -6767,10 +6767,10 @@
         <v>2020</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>285</v>
@@ -6779,16 +6779,16 @@
         <v>286</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>95.42</v>
+        <v>95.35</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>16</v>
@@ -6802,7 +6802,7 @@
         <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>287</v>
@@ -6811,16 +6811,16 @@
         <v>288</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>95.35</v>
+        <v>95.31</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>16</v>
@@ -6834,7 +6834,7 @@
         <v>13</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>289</v>
@@ -6843,16 +6843,16 @@
         <v>290</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>95.31</v>
+        <v>95.3</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>16</v>
@@ -6866,7 +6866,7 @@
         <v>13</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>291</v>
@@ -6875,16 +6875,16 @@
         <v>292</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>95.3</v>
+        <v>95.26</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>16</v>
@@ -6898,7 +6898,7 @@
         <v>13</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>293</v>
@@ -6907,16 +6907,16 @@
         <v>294</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>95.26</v>
+        <v>95.22</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>16</v>
@@ -6930,7 +6930,7 @@
         <v>13</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>295</v>
@@ -6939,16 +6939,16 @@
         <v>296</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>95.22</v>
+        <v>95.21</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>16</v>
@@ -6959,10 +6959,10 @@
         <v>2020</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>297</v>
@@ -6971,16 +6971,16 @@
         <v>298</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>95.21</v>
+        <v>95.19</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>16</v>
@@ -6994,7 +6994,7 @@
         <v>5</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>299</v>
@@ -7003,16 +7003,16 @@
         <v>300</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>95.19</v>
+        <v>95.17</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>16</v>
@@ -7023,10 +7023,10 @@
         <v>2020</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>301</v>
@@ -7035,16 +7035,16 @@
         <v>302</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>95.17</v>
+        <v>95.15</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>16</v>
@@ -7055,10 +7055,10 @@
         <v>2020</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>303</v>
@@ -7067,16 +7067,16 @@
         <v>304</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>95.15</v>
+        <v>95.13</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>16</v>
@@ -7090,7 +7090,7 @@
         <v>5</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>305</v>
@@ -7099,16 +7099,16 @@
         <v>306</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>95.13</v>
+        <v>95.12</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>16</v>
@@ -7122,7 +7122,7 @@
         <v>5</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>307</v>
@@ -7131,16 +7131,16 @@
         <v>308</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>95.12</v>
+        <v>95.11</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>16</v>
@@ -7151,10 +7151,10 @@
         <v>2020</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>309</v>
@@ -7163,16 +7163,16 @@
         <v>310</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>95.11</v>
+        <v>95.07</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>16</v>
@@ -7186,7 +7186,7 @@
         <v>13</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>311</v>
@@ -7195,10 +7195,10 @@
         <v>312</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
@@ -7215,10 +7215,10 @@
         <v>2020</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>313</v>
@@ -7227,16 +7227,16 @@
         <v>314</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>95.07</v>
+        <v>95.06</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>16</v>
@@ -7247,10 +7247,10 @@
         <v>2020</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>315</v>
@@ -7259,16 +7259,16 @@
         <v>316</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>95.06</v>
+        <v>95.05</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>16</v>
@@ -7279,10 +7279,10 @@
         <v>2020</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>317</v>
@@ -7291,16 +7291,16 @@
         <v>318</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>95.05</v>
+        <v>94.93</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>16</v>
@@ -7311,10 +7311,10 @@
         <v>2020</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>319</v>
@@ -7323,10 +7323,10 @@
         <v>320</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
@@ -7343,10 +7343,10 @@
         <v>2020</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>321</v>
@@ -7355,16 +7355,16 @@
         <v>322</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>94.93</v>
+        <v>94.92</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>16</v>
@@ -7375,10 +7375,10 @@
         <v>2020</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>323</v>
@@ -7387,16 +7387,16 @@
         <v>324</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>94.92</v>
+        <v>94.84</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>16</v>
@@ -7410,7 +7410,7 @@
         <v>13</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>325</v>
@@ -7419,16 +7419,16 @@
         <v>326</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>94.84</v>
+        <v>94.83</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>16</v>
@@ -7442,7 +7442,7 @@
         <v>13</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>327</v>
@@ -7451,16 +7451,16 @@
         <v>328</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>94.83</v>
+        <v>94.79</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>16</v>
@@ -7474,7 +7474,7 @@
         <v>13</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>329</v>
@@ -7483,10 +7483,10 @@
         <v>330</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
@@ -7503,10 +7503,10 @@
         <v>2020</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>331</v>
@@ -7515,16 +7515,16 @@
         <v>332</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>94.79</v>
+        <v>94.64</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>16</v>
@@ -7535,10 +7535,10 @@
         <v>2020</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>333</v>
@@ -7547,16 +7547,16 @@
         <v>334</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>94.64</v>
+        <v>94.63</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>16</v>
@@ -7567,10 +7567,10 @@
         <v>2020</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>335</v>
@@ -7579,16 +7579,16 @@
         <v>336</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>94.63</v>
+        <v>94.55</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>16</v>
@@ -7599,10 +7599,10 @@
         <v>2020</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>337</v>
@@ -7611,16 +7611,16 @@
         <v>338</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>94.55</v>
+        <v>94.41</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>16</v>
@@ -7634,7 +7634,7 @@
         <v>13</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>339</v>
@@ -7643,16 +7643,16 @@
         <v>340</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>94.41</v>
+        <v>94.4</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>16</v>
@@ -7663,10 +7663,10 @@
         <v>2020</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>341</v>
@@ -7675,16 +7675,16 @@
         <v>342</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>94.4</v>
+        <v>94.39</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>16</v>
@@ -7695,10 +7695,10 @@
         <v>2020</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>343</v>
@@ -7707,16 +7707,16 @@
         <v>344</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>94.39</v>
+        <v>94.35</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>16</v>
@@ -7730,7 +7730,7 @@
         <v>13</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>345</v>
@@ -7739,16 +7739,16 @@
         <v>346</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>94.35</v>
+        <v>94.18</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>16</v>
@@ -7759,10 +7759,10 @@
         <v>2020</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>347</v>
@@ -7771,16 +7771,16 @@
         <v>348</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>94.18</v>
+        <v>94.15</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>16</v>
@@ -7791,10 +7791,10 @@
         <v>2020</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>349</v>
@@ -7803,16 +7803,16 @@
         <v>350</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>94.15</v>
+        <v>94.07</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>16</v>
@@ -7823,10 +7823,10 @@
         <v>2020</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>351</v>
@@ -7835,16 +7835,16 @@
         <v>352</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>94.07</v>
+        <v>93.79</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>16</v>
@@ -7855,10 +7855,10 @@
         <v>2020</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>353</v>
@@ -7867,16 +7867,16 @@
         <v>354</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>93.79</v>
+        <v>93.78</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>16</v>
@@ -7887,10 +7887,10 @@
         <v>2020</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>355</v>
@@ -7899,16 +7899,16 @@
         <v>356</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>93.78</v>
+        <v>93.71</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>16</v>
@@ -7922,7 +7922,7 @@
         <v>5</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>357</v>
@@ -7931,16 +7931,16 @@
         <v>358</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>93.71</v>
+        <v>93.7</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>16</v>
@@ -7951,10 +7951,10 @@
         <v>2020</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>359</v>
@@ -7963,16 +7963,16 @@
         <v>360</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>93.7</v>
+        <v>93.65</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>16</v>
@@ -7986,7 +7986,7 @@
         <v>13</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>361</v>
@@ -7995,16 +7995,16 @@
         <v>362</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>93.65</v>
+        <v>93.58</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>16</v>
@@ -8018,7 +8018,7 @@
         <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>363</v>
@@ -8027,16 +8027,16 @@
         <v>364</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>93.58</v>
+        <v>93.55</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>16</v>
@@ -8050,7 +8050,7 @@
         <v>13</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>365</v>
@@ -8059,16 +8059,16 @@
         <v>366</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>93.55</v>
+        <v>93.51</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>16</v>
@@ -8082,7 +8082,7 @@
         <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>367</v>
@@ -8091,16 +8091,16 @@
         <v>368</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>93.51</v>
+        <v>93.22</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>16</v>
@@ -8111,10 +8111,10 @@
         <v>2020</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>369</v>
@@ -8123,16 +8123,16 @@
         <v>370</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>93.22</v>
+        <v>93.18</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>16</v>
@@ -8143,10 +8143,10 @@
         <v>2020</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>371</v>
@@ -8155,16 +8155,16 @@
         <v>372</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>93.18</v>
+        <v>93.17</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>16</v>
@@ -8175,10 +8175,10 @@
         <v>2020</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>373</v>
@@ -8187,16 +8187,16 @@
         <v>374</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>93.17</v>
+        <v>92.21</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>16</v>
@@ -8210,7 +8210,7 @@
         <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>375</v>
@@ -8219,16 +8219,16 @@
         <v>376</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>92.21</v>
+        <v>91.63</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>16</v>
@@ -8242,7 +8242,7 @@
         <v>13</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>377</v>
@@ -8251,16 +8251,16 @@
         <v>378</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>91.63</v>
+        <v>91.62</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>16</v>
@@ -8274,7 +8274,7 @@
         <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>379</v>
@@ -8283,16 +8283,16 @@
         <v>380</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>91.62</v>
+        <v>91.16</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>16</v>
@@ -8303,10 +8303,10 @@
         <v>2020</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>381</v>
@@ -8315,16 +8315,16 @@
         <v>382</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>91.16</v>
+        <v>90.66</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>16</v>
@@ -8338,7 +8338,7 @@
         <v>5</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>383</v>
@@ -8347,16 +8347,16 @@
         <v>384</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>90.66</v>
+        <v>90.14</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>16</v>
@@ -8367,10 +8367,10 @@
         <v>2020</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>385</v>
@@ -8379,16 +8379,16 @@
         <v>386</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>90.14</v>
+        <v>88.76</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>16</v>
@@ -8402,7 +8402,7 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>387</v>
@@ -8411,16 +8411,16 @@
         <v>388</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>88.76</v>
+        <v>86.05</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>16</v>
@@ -8434,7 +8434,7 @@
         <v>13</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>389</v>
@@ -8443,16 +8443,16 @@
         <v>390</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>86.05</v>
+        <v>85.11</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>16</v>
@@ -8463,28 +8463,28 @@
         <v>2020</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>106</v>
+        <v>391</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>49</v>
+        <v>394</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>50</v>
+        <v>395</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>85.11</v>
+        <v>98.06</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>16</v>
@@ -8498,25 +8498,25 @@
         <v>4</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D187" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="F187" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="E187" s="2" t="s">
+      <c r="G187" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="F187" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="G187" s="2" t="s">
-        <v>397</v>
-      </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>98.06</v>
+        <v>97.88</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>16</v>
@@ -8527,28 +8527,28 @@
         <v>2020</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>97.88</v>
+        <v>97.62</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>16</v>
@@ -8559,28 +8559,28 @@
         <v>2020</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>97.62</v>
+        <v>97.08</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>16</v>
@@ -8591,10 +8591,10 @@
         <v>2020</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>404</v>
@@ -8603,16 +8603,16 @@
         <v>405</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>97.08</v>
+        <v>97.05</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>16</v>
@@ -8626,7 +8626,7 @@
         <v>4</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>406</v>
@@ -8635,16 +8635,16 @@
         <v>407</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>97.05</v>
+        <v>96.96</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>16</v>
@@ -8655,28 +8655,28 @@
         <v>2020</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>96.96</v>
+        <v>96.94</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>16</v>
@@ -8687,10 +8687,10 @@
         <v>2020</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>411</v>
@@ -8699,16 +8699,16 @@
         <v>412</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>96.94</v>
+        <v>96.82</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>16</v>
@@ -8722,7 +8722,7 @@
         <v>4</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>413</v>
@@ -8731,16 +8731,16 @@
         <v>414</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>96.82</v>
+        <v>96.63</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>16</v>
@@ -8751,10 +8751,10 @@
         <v>2020</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>415</v>
@@ -8763,16 +8763,16 @@
         <v>416</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>96.63</v>
+        <v>96.6</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>16</v>
@@ -8786,7 +8786,7 @@
         <v>3</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>417</v>
@@ -8795,16 +8795,16 @@
         <v>418</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>96.6</v>
+        <v>96.54</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>16</v>
@@ -8818,7 +8818,7 @@
         <v>3</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>419</v>
@@ -8827,10 +8827,10 @@
         <v>420</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
@@ -8850,7 +8850,7 @@
         <v>3</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>421</v>
@@ -8859,16 +8859,16 @@
         <v>422</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>96.54</v>
+        <v>96.53</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>16</v>
@@ -8882,7 +8882,7 @@
         <v>3</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>423</v>
@@ -8891,16 +8891,16 @@
         <v>424</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>96.53</v>
+        <v>96.46</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>16</v>
@@ -8911,28 +8911,28 @@
         <v>2020</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>96.46</v>
+        <v>96.45</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>16</v>
@@ -8943,10 +8943,10 @@
         <v>2020</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>427</v>
+        <v>391</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>428</v>
@@ -8955,16 +8955,16 @@
         <v>429</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>96.45</v>
+        <v>96.33</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>16</v>
@@ -8978,7 +8978,7 @@
         <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>430</v>
@@ -8987,16 +8987,16 @@
         <v>431</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>96.33</v>
+        <v>96.29</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>16</v>
@@ -9010,7 +9010,7 @@
         <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>432</v>
@@ -9019,10 +9019,10 @@
         <v>433</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
@@ -9042,7 +9042,7 @@
         <v>4</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>434</v>
@@ -9051,16 +9051,16 @@
         <v>435</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>96.29</v>
+        <v>96.21</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>16</v>
@@ -9071,10 +9071,10 @@
         <v>2020</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>436</v>
@@ -9083,16 +9083,16 @@
         <v>437</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>96.21</v>
+        <v>96.04</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>16</v>
@@ -9103,10 +9103,10 @@
         <v>2020</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>438</v>
@@ -9115,16 +9115,16 @@
         <v>439</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>96.04</v>
+        <v>96.01</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>16</v>
@@ -9135,10 +9135,10 @@
         <v>2020</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>440</v>
@@ -9147,16 +9147,16 @@
         <v>441</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>96.01</v>
+        <v>95.7</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>16</v>
@@ -9167,10 +9167,10 @@
         <v>2020</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>442</v>
@@ -9179,16 +9179,16 @@
         <v>443</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>95.7</v>
+        <v>95.26</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>16</v>
@@ -9199,10 +9199,10 @@
         <v>2020</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>444</v>
@@ -9211,16 +9211,16 @@
         <v>445</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>95.26</v>
+        <v>95.14</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>16</v>
@@ -9231,28 +9231,28 @@
         <v>2020</v>
       </c>
       <c r="B210" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>446</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>447</v>
+        <v>391</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>95.14</v>
+        <v>94.91</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>16</v>
@@ -9263,28 +9263,28 @@
         <v>2020</v>
       </c>
       <c r="B211" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>393</v>
+        <v>425</v>
       </c>
       <c r="D211" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E211" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="E211" s="2" t="s">
-        <v>393</v>
-      </c>
       <c r="F211" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>94.91</v>
+        <v>94.81</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>16</v>
@@ -9295,10 +9295,10 @@
         <v>2020</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>449</v>
@@ -9307,16 +9307,16 @@
         <v>450</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>94.81</v>
+        <v>94.73</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>16</v>
@@ -9327,10 +9327,10 @@
         <v>2020</v>
       </c>
       <c r="B213" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>451</v>
@@ -9339,16 +9339,16 @@
         <v>452</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>94.73</v>
+        <v>94.63</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>16</v>
@@ -9359,10 +9359,10 @@
         <v>2020</v>
       </c>
       <c r="B214" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>453</v>
@@ -9371,16 +9371,16 @@
         <v>454</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>94.63</v>
+        <v>94.3</v>
       </c>
       <c r="J214" s="2" t="s">
         <v>16</v>
@@ -9391,10 +9391,10 @@
         <v>2020</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>455</v>
@@ -9403,16 +9403,16 @@
         <v>456</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>94.3</v>
+        <v>94.18</v>
       </c>
       <c r="J215" s="2" t="s">
         <v>16</v>
@@ -9423,10 +9423,10 @@
         <v>2020</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>457</v>
@@ -9435,16 +9435,16 @@
         <v>458</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>94.18</v>
+        <v>93.96</v>
       </c>
       <c r="J216" s="2" t="s">
         <v>16</v>
@@ -9455,10 +9455,10 @@
         <v>2020</v>
       </c>
       <c r="B217" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>427</v>
+        <v>398</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>459</v>
@@ -9467,16 +9467,16 @@
         <v>460</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>93.96</v>
+        <v>93.58</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>16</v>
@@ -9487,10 +9487,10 @@
         <v>2020</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>461</v>
@@ -9499,16 +9499,16 @@
         <v>462</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>93.58</v>
+        <v>93.48</v>
       </c>
       <c r="J218" s="2" t="s">
         <v>16</v>
@@ -9519,28 +9519,28 @@
         <v>2020</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>427</v>
+        <v>398</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>463</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>464</v>
+        <v>398</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>93.48</v>
+        <v>93.3</v>
       </c>
       <c r="J219" s="2" t="s">
         <v>16</v>
@@ -9551,28 +9551,28 @@
         <v>2020</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="D220" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E220" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="E220" s="2" t="s">
-        <v>400</v>
-      </c>
       <c r="F220" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>93.3</v>
+        <v>92.46</v>
       </c>
       <c r="J220" s="2" t="s">
         <v>16</v>
@@ -9583,10 +9583,10 @@
         <v>2020</v>
       </c>
       <c r="B221" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>427</v>
+        <v>398</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>466</v>
@@ -9595,16 +9595,16 @@
         <v>467</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>92.46</v>
+        <v>92.31</v>
       </c>
       <c r="J221" s="2" t="s">
         <v>16</v>
@@ -9615,10 +9615,10 @@
         <v>2020</v>
       </c>
       <c r="B222" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>468</v>
@@ -9627,16 +9627,16 @@
         <v>469</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>92.31</v>
+        <v>92.17</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>16</v>
@@ -9647,10 +9647,10 @@
         <v>2020</v>
       </c>
       <c r="B223" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>470</v>
@@ -9659,16 +9659,16 @@
         <v>471</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>92.17</v>
+        <v>92.14</v>
       </c>
       <c r="J223" s="2" t="s">
         <v>16</v>
@@ -9679,10 +9679,10 @@
         <v>2020</v>
       </c>
       <c r="B224" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>427</v>
+        <v>391</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>472</v>
@@ -9691,16 +9691,16 @@
         <v>473</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>92.14</v>
+        <v>91.99</v>
       </c>
       <c r="J224" s="2" t="s">
         <v>16</v>
@@ -9714,7 +9714,7 @@
         <v>2</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>474</v>
@@ -9723,10 +9723,10 @@
         <v>475</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9746,7 +9746,7 @@
         <v>2</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>476</v>
@@ -9755,10 +9755,10 @@
         <v>477</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_basneta_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_basneta_a_2020.xlsx
@@ -2116,7 +2116,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:08</t>
+    <t xml:space="preserve">2026-09-18 11:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_basneta_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_basneta_a_2020.xlsx
@@ -2116,7 +2116,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:29</t>
+    <t xml:space="preserve">2026-09-24 00:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
